--- a/BUFF库.xlsx
+++ b/BUFF库.xlsx
@@ -52,7 +52,7 @@
     <t>滑稽</t>
   </si>
   <si>
-    <t>拥有者在自己的回合开始时自动对随机敌人造成40点伤害，最高只能获得一层，战斗结束后清零</t>
+    <t>拥有者在自己的回合开始时自动对随机敌人造成40点伤害</t>
   </si>
   <si>
     <t>虚弱</t>

--- a/BUFF库.xlsx
+++ b/BUFF库.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>BUFF名称</t>
   </si>
@@ -92,6 +92,12 @@
   </si>
   <si>
     <t>拥有者减少S点防御（S为拥有的破防层数），战斗结束清零</t>
+  </si>
+  <si>
+    <t>流血</t>
+  </si>
+  <si>
+    <t>束缚</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1028,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1126,6 +1132,16 @@
       </c>
       <c r="C9" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
